--- a/data/trans_bre/P1427-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1427-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,48</t>
+          <t>-0,81; 2,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,5</t>
+          <t>-0,34; 2,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,81</t>
+          <t>0,26; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 183,05</t>
+          <t>-29,85; 185,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 306,45</t>
+          <t>-27,88; 286,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 106,53</t>
+          <t>5,08; 111,48</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,07</t>
+          <t>-0,92; 2,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,88</t>
+          <t>-0,01; 1,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,41</t>
+          <t>-1,23; 1,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 145,42</t>
+          <t>-31,31; 156,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 450,35</t>
+          <t>-7,22; 415,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 165,6</t>
+          <t>-31,38; 53,65</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>110,94%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,42</t>
+          <t>-0,46; 2,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,52</t>
+          <t>-0,24; 2,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,86</t>
+          <t>0,78; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 271,95</t>
+          <t>-28,73; 319,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 511,06</t>
+          <t>-31,72; 514,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 159,02</t>
+          <t>19,55; 259,48</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,92</t>
+          <t>-1,02; 2,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,29</t>
+          <t>0,63; 3,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,21</t>
+          <t>-0,08; 2,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 122,15</t>
+          <t>-34,77; 125,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,98; 412,68</t>
+          <t>30,22; 466,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 123,77</t>
+          <t>-2,43; 110,04</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,51</t>
+          <t>-0,1; 1,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,86</t>
+          <t>0,61; 1,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,21</t>
+          <t>0,62; 2,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 89,81</t>
+          <t>-4,5; 87,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,08; 232,04</t>
+          <t>45,71; 224,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 85,86</t>
+          <t>17,26; 73,34</t>
         </is>
       </c>
     </row>
